--- a/EASYCIVIL.bundle/CONTENTS/NET8/EASYCIVILCOMMANDS.xlsx
+++ b/EASYCIVIL.bundle/CONTENTS/NET8/EASYCIVILCOMMANDS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CIVIL3D.NET\CIVIL3D ONE PROJECT\EASYCIVIL\MENU\EASYCIVILMENU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AUTOLISP\CIVIL3D.NET\CIVIL3D ONE PROJECT\EASYCIVIL\MENU\EASYCIVILMENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD44DA-9FCC-4A48-A7DD-F9CCA170A4B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CB6488-0E71-4890-914C-C775B12DE1F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="12645" tabRatio="748" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="12645" tabRatio="748" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="119">
   <si>
     <t>SPP</t>
   </si>
@@ -391,6 +391,12 @@
   </si>
   <si>
     <t>[ADP]..Auto Add Parts to Profile</t>
+  </si>
+  <si>
+    <t>SMP</t>
+  </si>
+  <si>
+    <t>[SMP]..Total Length Of Pipes</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2107C9-EFD4-4E4B-9413-26B6D64F3288}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1203,38 +1209,46 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
     </row>

--- a/EASYCIVIL.bundle/CONTENTS/NET8/EASYCIVILCOMMANDS.xlsx
+++ b/EASYCIVIL.bundle/CONTENTS/NET8/EASYCIVILCOMMANDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AUTOLISP\CIVIL3D.NET\CIVIL3D ONE PROJECT\EASYCIVIL\MENU\EASYCIVILMENU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AUTOLISP\CIVIL3D.NET\CIVIL3D ONE PROJECT\EASYCIVIL\MENU\EASYCIVILMENU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CB6488-0E71-4890-914C-C775B12DE1F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A56E0D2-0945-4D80-8B5D-A3C2040386C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="12645" tabRatio="748" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="12645" tabRatio="748" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="8" r:id="rId1"/>
@@ -297,12 +297,6 @@
     <t>[CPH]..Move Path Of Pressure or Pipe Network</t>
   </si>
   <si>
-    <t>MKC</t>
-  </si>
-  <si>
-    <t>[MKC]..Mark Clashes</t>
-  </si>
-  <si>
     <t>[ACPP]..Auto Connect Pressure Pipe</t>
   </si>
   <si>
@@ -354,12 +348,6 @@
     <t>[FFF]..Fillter Selection</t>
   </si>
   <si>
-    <t>OPCR</t>
-  </si>
-  <si>
-    <t>[OPCR]..Open Clash Report</t>
-  </si>
-  <si>
     <t>EASYCIVILABOUTLICENSE</t>
   </si>
   <si>
@@ -397,6 +385,18 @@
   </si>
   <si>
     <t>[SMP]..Total Length Of Pipes</t>
+  </si>
+  <si>
+    <t>RSS</t>
+  </si>
+  <si>
+    <t>[RSS]..Resolve Pipes Not Selected</t>
+  </si>
+  <si>
+    <t>CNV</t>
+  </si>
+  <si>
+    <t>[CNV]..Clash Navigation</t>
   </si>
 </sst>
 </file>
@@ -768,10 +768,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -883,10 +883,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1038,10 +1038,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1061,18 +1061,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2107C9-EFD4-4E4B-9413-26B6D64F3288}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1201,18 +1201,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1225,15 +1225,15 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1250,6 +1250,19 @@
       </c>
       <c r="B11" s="2" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1313,10 +1326,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1347,10 +1360,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1360,26 +1373,26 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1441,10 +1454,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1452,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1524,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05290D9-923D-4D36-93C8-988364A60A05}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1534,23 +1547,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
